--- a/docs/산출물/09_한결공조_AS관리_통합테스트결과서_V1.0.xlsx
+++ b/docs/산출물/09_한결공조_AS관리_통합테스트결과서_V1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\my-first-project\docs\산출물\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E68CA652-82F3-4A95-B833-F44CE7CB27CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F7E7193-0200-43A4-8703-5C3360421A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="353">
   <si>
     <t>프로젝트명</t>
   </si>
@@ -1328,7 +1328,7 @@
     <t>• "사용할 수 없음" 안내</t>
   </si>
   <si>
-    <t>실제 화면 확인 기록 없음 (Apex 테스트 rejectTechnician 계열 Pass)</t>
+    <t>2026-10-16: 최민호 화면에서 입력 없이 안내만 표시 확인(Edwin)</t>
   </si>
   <si>
     <t>PROCESS 2 · 출동 · 사용 부품 (센터장 · 기사)</t>
@@ -1356,7 +1356,10 @@
     <t>• 출동 생성, 기사에게만 보임</t>
   </si>
   <si>
-    <t>이번 확인 기간 실제 화면 기록 없음 (시연 출동은 관리자가 생성)</t>
+    <t>리허설 예정 (샌드박스 리허설 때 확인 후 기입)</t>
+  </si>
+  <si>
+    <t>리허설 예정</t>
   </si>
   <si>
     <t>출동 사용 부품</t>
@@ -1404,7 +1407,7 @@
     <t>• "차량 재고가 부족합니다" 거부</t>
   </si>
   <si>
-    <t>실제 화면 확인 기록 없음 (Apex 테스트 VanStockService·WorkOrderPartsController Pass)</t>
+    <t>리허설 예정 (Apex 테스트 VanStockService·WorkOrderPartsController는 Pass)</t>
   </si>
   <si>
     <t>PROCESS 3 · 출동 승인 (기사 · 센터장)</t>
@@ -1431,7 +1434,7 @@
     <t>• "승인이 필요하지 않습니다" 안내</t>
   </si>
   <si>
-    <t>실제 화면 확인 기록 없음</t>
+    <t>2026-10-16: 최민호 화면에서 "승인이 필요하지 않습니다" 안내 확인(Edwin)</t>
   </si>
   <si>
     <t>기사 승인 요청 제출</t>
@@ -1453,10 +1456,7 @@
     <t>• 상태 승인 대기, 승인자 김병철</t>
   </si>
   <si>
-    <t>2026-10-15 17:46: 최민호 제출(사유 "고객 과실", 고객 동의 저장), 승인자 김병철 — org 승인 기록. 제출 경로(빠른 작업 / 승인 내역 버튼)는 기록으로 구분 안 됨</t>
-  </si>
-  <si>
-    <t>제출 경로 확인 필요</t>
+    <t>2026-10-15 17:46: 최민호 제출(사유 "고객 과실", 고객 동의 저장), 승인자 김병철 — org 승인 기록. 출동의 [승인 요청] 빠른 작업으로 제출(Edwin)</t>
   </si>
   <si>
     <t>출동 승인</t>
@@ -1522,10 +1522,10 @@
     <t>• [승인 요청] 버튼 표시</t>
   </si>
   <si>
-    <t>2026-10-15 사용자 보고: 버튼이 보이지 않음. 기사 권한 집합·프로필에 Flow 실행 권한 없음(조회) — 해결 결정 대기</t>
-  </si>
-  <si>
-    <t>수정사항관리 결함</t>
+    <t>2026-10-15 버튼 미표시 → 원인: 출동 피드 추적으로 빠른 작업이 Chatter 게시자 영역에 배치(페이지에 피드 없음). 강조 표시 패널을 동적 작업으로 전환 후 최민호 화면에서 표시 확인. Flow 실행 권한은 추가하지 않음(개별 Flow 접근만으로 동작)</t>
+  </si>
+  <si>
+    <t>결함 수정 후 재확인</t>
   </si>
   <si>
     <t>PROCESS 4 · 외부 연동 (ERP · 주소)</t>
@@ -1672,7 +1672,7 @@
     <t>• ErpSyncStatus__c = Synced</t>
   </si>
   <si>
-    <t>org에 재고 이동 기록 0건 — 실제 연동 미확인 (Apex 테스트 ProductTransferTriggerHandler Pass)</t>
+    <t>리허설 예정 (org 재고 이동 기록 0건, Apex 테스트 ProductTransferTriggerHandler는 Pass)</t>
   </si>
   <si>
     <t>IF-06</t>
@@ -1891,10 +1891,10 @@
     <t>HG_ErpIntegrationData</t>
   </si>
   <si>
-    <t>협력 기사 화면에 [승인 요청] 빠른 작업이 보이지 않음 → 기사 권한 집합에 Flow 실행 권한 없음으로 추정</t>
-  </si>
-  <si>
-    <t>해결 방법(Run Flows 추가 / Flow User) 결정 대기</t>
+    <t>협력 기사 화면에 [승인 요청] 빠른 작업이 보이지 않음 → 원인: 출동 피드 추적이 켜져 빠른 작업이 Chatter 게시자 영역에 배치됐는데 출동 레코드 페이지에 피드 구성 요소가 없음. 강조 표시 패널을 동적 작업으로 전환(편집·승인 요청·소유자 변경·복제·삭제)</t>
+  </si>
+  <si>
+    <t>처음 추정(Flow 실행 권한)은 원인 아님. 최민호 화면 확인</t>
   </si>
   <si>
     <t>사용 부품 삭제</t>
@@ -1927,7 +1927,7 @@
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
-    <t>기사 [승인 요청] 빠른 작업 미표시 1건 결정 대기</t>
+    <t>리허설 예정 3건(센터장 출동 배정·재고 초과 화면·재고 이동 ERP)</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
@@ -3300,18 +3300,18 @@
       </c>
       <c r="E9" s="68">
         <f>COUNTIFS(수정사항관리!$A:$A, "통합 테스트 (1차)", 수정사항관리!$K:$K, "완료")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" s="68">
         <f>D9-E9</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="72">
         <f>IFERROR(E9/D9, 0)</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H9" s="68" t="s">
-        <v>308</v>
+        <v>14</v>
       </c>
       <c r="I9" s="94" t="s">
         <v>349</v>
@@ -3388,15 +3388,15 @@
       </c>
       <c r="E12" s="74">
         <f>SUM(E8:E11)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F12" s="74">
         <f>SUM(F8:F11)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" s="75">
         <f>IFERROR(E12/D12, 0)</f>
-        <v>0.84615384615384615</v>
+        <v>0.92307692307692313</v>
       </c>
       <c r="H12" s="74"/>
       <c r="I12" s="74"/>
@@ -3713,23 +3713,23 @@
       </c>
       <c r="B9" s="28">
         <f>COUNTIF('통합테스트 시나리오'!$M$4:$M$272, "Pass")</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C9" s="29">
         <f>COUNTIF('통합테스트 시나리오'!$M$4:$M$272, "Fail")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="30">
         <f>A9-B9-C9</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E9" s="31">
         <f>IFERROR(B9/(B9+C9), 0)</f>
-        <v>0.93333333333333335</v>
+        <v>1</v>
       </c>
       <c r="F9" s="31">
         <f>IFERROR((B9+C9)/A9, 0)</f>
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="G9" s="32" t="str">
         <f>IF(F9&lt;1, "진행 중", IF(E9&gt;=0.95, "✓ Pass", IF(E9&gt;=0.8, "△ 조건부", "✗ Fail")))</f>
@@ -3811,7 +3811,7 @@
       </c>
       <c r="D14" s="60">
         <f>COUNTIFS('통합테스트 시나리오'!$B$4:$B$272, "1", '통합테스트 시나리오'!$M$4:$M$272, "Pass")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" s="61">
         <f>COUNTIFS('통합테스트 시나리오'!$B$4:$B$272, "1", '통합테스트 시나리오'!$M$4:$M$272, "Fail")</f>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="F14" s="34">
         <f>C14-D14-E14</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="62">
         <f>IFERROR(D14/(D14+E14), 0)</f>
@@ -3867,19 +3867,19 @@
       </c>
       <c r="D16" s="60">
         <f>COUNTIFS('통합테스트 시나리오'!$B$4:$B$272, "3", '통합테스트 시나리오'!$M$4:$M$272, "Pass")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" s="61">
         <f>COUNTIFS('통합테스트 시나리오'!$B$4:$B$272, "3", '통합테스트 시나리오'!$M$4:$M$272, "Fail")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="34">
         <f>C16-D16-E16</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="62">
         <f>IFERROR(D16/(D16+E16), 0)</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="24" customHeight="1">
@@ -4000,7 +4000,7 @@
     </row>
     <row r="23" spans="1:7" ht="24" customHeight="1">
       <c r="A23" s="33" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B23" s="35" t="s">
         <v>284</v>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="F30" s="37">
         <f>COUNTIF(수정사항관리!$K$5:$K$200, "진행 중")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="21.75" customHeight="1">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="F31" s="37">
         <f>COUNTIF(수정사항관리!$K$5:$K$200, "완료")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="21.75" customHeight="1">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="E7" s="38">
         <f>COUNTIFS('통합테스트 시나리오'!$B$4:$B$272, "1", '통합테스트 시나리오'!$M$4:$M$272, "Pass")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" s="38">
         <f>COUNTIFS('통합테스트 시나리오'!$B$4:$B$272, "1", '통합테스트 시나리오'!$M$4:$M$272, "Fail")</f>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="G7" s="38">
         <f>D7-E7-F7</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="40">
         <f>IFERROR(E7/(E7+F7), 0)</f>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="E8" s="43">
         <f>COUNTIFS('통합테스트 시나리오'!$B$4:$B$272, "1", '통합테스트 시나리오'!$E$4:$E$272, C8, '통합테스트 시나리오'!$M$4:$M$272, "Pass")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="44">
         <f>COUNTIFS('통합테스트 시나리오'!$B$4:$B$272, "1", '통합테스트 시나리오'!$E$4:$E$272, C8, '통합테스트 시나리오'!$M$4:$M$272, "Fail")</f>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G8" s="63">
         <f>D8-E8-F8</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="45">
         <f>IFERROR(E8/(E8+F8), 0)</f>
@@ -4520,10 +4520,10 @@
         <v>2</v>
       </c>
       <c r="B13" s="41" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C13" s="42" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D13" s="42">
         <f>COUNTIFS('통합테스트 시나리오'!$B$4:$B$272, "2", '통합테스트 시나리오'!$E$4:$E$272, C13)</f>
@@ -4561,19 +4561,19 @@
       </c>
       <c r="E15" s="38">
         <f>COUNTIFS('통합테스트 시나리오'!$B$4:$B$272, "3", '통합테스트 시나리오'!$M$4:$M$272, "Pass")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F15" s="38">
         <f>COUNTIFS('통합테스트 시나리오'!$B$4:$B$272, "3", '통합테스트 시나리오'!$M$4:$M$272, "Fail")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="38">
         <f>D15-E15-F15</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="40">
         <f>IFERROR(E15/(E15+F15), 0)</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="21.75" customHeight="1">
@@ -4581,10 +4581,10 @@
         <v>1</v>
       </c>
       <c r="B16" s="41" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C16" s="42" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D16" s="42">
         <f>COUNTIFS('통합테스트 시나리오'!$B$4:$B$272, "3", '통합테스트 시나리오'!$E$4:$E$272, C16)</f>
@@ -4592,19 +4592,19 @@
       </c>
       <c r="E16" s="43">
         <f>COUNTIFS('통합테스트 시나리오'!$B$4:$B$272, "3", '통합테스트 시나리오'!$E$4:$E$272, C16, '통합테스트 시나리오'!$M$4:$M$272, "Pass")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16" s="44">
         <f>COUNTIFS('통합테스트 시나리오'!$B$4:$B$272, "3", '통합테스트 시나리오'!$E$4:$E$272, C16, '통합테스트 시나리오'!$M$4:$M$272, "Fail")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="63">
         <f>D16-E16-F16</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" s="45">
         <f>IFERROR(E16/(E16+F16), 0)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="21.75" customHeight="1">
@@ -5188,13 +5188,13 @@
       <c r="L11" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="M11" s="21"/>
+      <c r="M11" s="21" t="s">
+        <v>35</v>
+      </c>
       <c r="N11" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="O11" s="21" t="s">
-        <v>37</v>
-      </c>
+      <c r="O11" s="21"/>
       <c r="P11" s="21"/>
     </row>
     <row r="12" spans="2:16" ht="17.25">
@@ -5216,7 +5216,7 @@
       <c r="O12" s="21"/>
       <c r="P12" s="21"/>
     </row>
-    <row r="13" spans="2:16" ht="86.25">
+    <row r="13" spans="2:16" ht="69">
       <c r="B13" s="19">
         <v>2</v>
       </c>
@@ -5253,7 +5253,7 @@
         <v>108</v>
       </c>
       <c r="O13" s="21" t="s">
-        <v>37</v>
+        <v>166</v>
       </c>
       <c r="P13" s="21"/>
     </row>
@@ -5266,28 +5266,28 @@
         <v>8</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H14" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J14" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K14" s="21" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L14" s="21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M14" s="21" t="s">
         <v>35</v>
@@ -5296,13 +5296,13 @@
         <v>108</v>
       </c>
       <c r="O14" s="21" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P14" s="21" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="15" spans="2:16" ht="138">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" ht="120.75">
       <c r="B15" s="19">
         <v>2</v>
       </c>
@@ -5311,35 +5311,35 @@
         <v>9</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G15" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I15" s="21" t="s">
         <v>153</v>
       </c>
       <c r="J15" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K15" s="21" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L15" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M15" s="21"/>
       <c r="N15" s="21" t="s">
         <v>108</v>
       </c>
       <c r="O15" s="21" t="s">
-        <v>37</v>
+        <v>166</v>
       </c>
       <c r="P15" s="21"/>
     </row>
@@ -5347,7 +5347,7 @@
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
       <c r="D16" s="20" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E16" s="21"/>
       <c r="F16" s="21"/>
@@ -5362,7 +5362,7 @@
       <c r="O16" s="21"/>
       <c r="P16" s="21"/>
     </row>
-    <row r="17" spans="2:16" ht="51.75">
+    <row r="17" spans="2:16" ht="86.25">
       <c r="B17" s="19">
         <v>3</v>
       </c>
@@ -5371,39 +5371,39 @@
         <v>10</v>
       </c>
       <c r="E17" s="21" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G17" s="21" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I17" s="21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J17" s="21" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K17" s="21" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="M17" s="21"/>
+        <v>191</v>
+      </c>
+      <c r="M17" s="21" t="s">
+        <v>35</v>
+      </c>
       <c r="N17" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="O17" s="21" t="s">
-        <v>37</v>
-      </c>
+      <c r="O17" s="21"/>
       <c r="P17" s="21"/>
     </row>
-    <row r="18" spans="2:16" ht="189.75">
+    <row r="18" spans="2:16" ht="172.5">
       <c r="B18" s="19">
         <v>3</v>
       </c>
@@ -5412,28 +5412,28 @@
         <v>11</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G18" s="21" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H18" s="21" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I18" s="21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J18" s="21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K18" s="21" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L18" s="21" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M18" s="21" t="s">
         <v>35</v>
@@ -5441,9 +5441,7 @@
       <c r="N18" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="O18" s="21" t="s">
-        <v>198</v>
-      </c>
+      <c r="O18" s="21"/>
       <c r="P18" s="21"/>
     </row>
     <row r="19" spans="2:16" ht="138">
@@ -5530,7 +5528,7 @@
       </c>
       <c r="P20" s="21"/>
     </row>
-    <row r="21" spans="2:16" ht="138">
+    <row r="21" spans="2:16" ht="293.25">
       <c r="B21" s="19">
         <v>3</v>
       </c>
@@ -5539,7 +5537,7 @@
         <v>14</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F21" s="21" t="s">
         <v>215</v>
@@ -5563,7 +5561,7 @@
         <v>220</v>
       </c>
       <c r="M21" s="21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N21" s="21" t="s">
         <v>108</v>
@@ -5675,7 +5673,7 @@
       </c>
       <c r="O24" s="21"/>
       <c r="P24" s="21" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25" spans="2:16" ht="120.75">
@@ -5720,7 +5718,7 @@
         <v>247</v>
       </c>
       <c r="P25" s="21" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26" spans="2:16" ht="155.25">
@@ -5762,7 +5760,7 @@
         <v>108</v>
       </c>
       <c r="O26" s="21" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P26" s="21" t="s">
         <v>255</v>
@@ -5848,7 +5846,7 @@
         <v>108</v>
       </c>
       <c r="O28" s="21" t="s">
-        <v>37</v>
+        <v>166</v>
       </c>
       <c r="P28" s="21" t="s">
         <v>271</v>
@@ -10201,7 +10199,7 @@
     </row>
     <row r="6" spans="1:8" ht="27.75" customHeight="1">
       <c r="A6" s="64" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>284</v>
@@ -10670,7 +10668,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D8" s="58" t="s">
         <v>323</v>
@@ -10818,7 +10816,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D12" s="58" t="s">
         <v>331</v>
@@ -10924,7 +10922,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="57" customFormat="1" ht="27">
+    <row r="15" spans="1:12" s="57" customFormat="1" ht="40.5">
       <c r="A15" s="56" t="s">
         <v>27</v>
       </c>
@@ -10932,7 +10930,7 @@
         <v>11</v>
       </c>
       <c r="C15" s="56" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D15" s="56" t="s">
         <v>338</v>
@@ -10949,10 +10947,14 @@
       <c r="H15" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="I15" s="77"/>
-      <c r="J15" s="77"/>
+      <c r="I15" s="77">
+        <v>46311</v>
+      </c>
+      <c r="J15" s="77">
+        <v>46311</v>
+      </c>
       <c r="K15" s="56" t="s">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="L15" s="56" t="s">
         <v>339</v>
